--- a/MEDIA/FOOTAGE/key_footage.xlsx
+++ b/MEDIA/FOOTAGE/key_footage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.93.91.25\IDEX_Artifacts\MEDIA\FOOTAGE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\MEDIA\FOOTAGE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3F25819-CF38-4BC3-BC67-382D8A44144E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78D4D4AA-4527-40E8-8A42-054AD4AC71A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30075" yWindow="510" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="64">
   <si>
     <t>IDEX_2023_07_14_MEM_CAMA_c01</t>
   </si>
@@ -205,6 +205,18 @@
   </si>
   <si>
     <t>Fort Hall</t>
+  </si>
+  <si>
+    <t>IDEX_2026_02_03_AMM_CAMa_c1</t>
+  </si>
+  <si>
+    <t>Misc</t>
+  </si>
+  <si>
+    <t>Adam McCoy</t>
+  </si>
+  <si>
+    <t>Capitol Artifacts - Nike, Washington, Model Train, Territory Capitol Painting</t>
   </si>
 </sst>
 </file>
@@ -524,7 +536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.42578125" bestFit="1" customWidth="1"/>
@@ -944,6 +956,26 @@
         <v>58</v>
       </c>
     </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" t="s">
+        <v>52</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G23" t="s">
+        <v>63</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
